--- a/p6_deployment/data/italy/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/italy/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>0OKRs71U</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>4W5t03Zl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>rN4paNle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6Le197C2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>jPP565dL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>pnP95PBR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CYQ17osF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pCf58RR8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hI7JpOZ1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Cd9lbs41</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>M7Gy1qKr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rmlyYpjd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Q7Nvh6sS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nHOzgnSL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>beWNelr3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hZVgSCF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>vF3Fo4Ke</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IaF6mQkq</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>djEAnp5k</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>hIVRf8c9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>K4XJdUSd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UFIypiqi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>jk9duTcM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GCUgL76j</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>4YAlskT9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>QsCprVD3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>4dkXYQzj</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>CbAht9rG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YDb1vmDS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>AZkTZ6Lq</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>rJMuqBbc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>MBCLwGMH</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>jDeAtIxa</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>8l65sbNh</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>0O2cqKht</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>bFGVm0pP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>xMVkMmip</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>fsjku8tP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>lbEDuxh5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Uc71rv8n</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>rLDHvd7B</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>dQhciEZJ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>tvnotlRI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>8QmwrAd6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SEWuqjs0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>nHnssUBC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>zHi1jYlQ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>f1YXpCCm</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>tbUTohcs</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>lOXypWRg</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>8AaFSUdJ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>f1nTGXc7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>rNSNxFKQ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>279fXhrl</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pWEkYYSs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>tb8bWCcf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>neB6UjS6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>zL72VWC0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>UJ0BTAsD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>zcPFvyjE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>YioXFiDD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>l0TJwe5K</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>K6Cj3ET7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>C0axRHLE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>UyfsQyyL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>MZYLIgTf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>vBqHJZDl</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Y90YRc68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>0QXPHDr1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Q7uDKFbr</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>8ShoPejR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Q7Js5zae</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>pjacQpV3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>CpeE3NNj</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>8W8n4fE1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>tIh6OOaG</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>jTagRQFc</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>Cx1kS60i</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>IsGZ6dUr</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>bg31P4pA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>nHKw6Gqk</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>CMCRCR04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>KnGZA5VG</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>hM5FFTGo</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>GE9r9q0T</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>vJHXjpvo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>j7OIEmWi</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>tdHVBoGA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>YVDND7ob</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>YgdA438p</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2B5vAPpN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>C2pt1U1h</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>nLxgbSoB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>xAV5eQVT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>jgqp0lHb</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>4xox2Ann</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>trxccn1H</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>YHYla8W4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>KYz1d6GN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>QonY2jXu</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>